--- a/ig/acknowledgement/all-profiles.xlsx
+++ b/ig/acknowledgement/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5492" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5458" uniqueCount="593">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.2</t>
+    <t>2.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T12:26:02+01:00</t>
+    <t>2026-02-05T13:48:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>MedCom (http://www.medcom.dk)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -349,7 +349,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -564,7 +564,7 @@
     <t>A code that provides details as the exact issue.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/operation-outcome</t>
+    <t>http://hl7.org/fhir/ValueSet/operation-outcome|4.0.1</t>
   </si>
   <si>
     <t>OperationOutcome.issue.details.id</t>
@@ -704,6 +704,9 @@
   </si>
   <si>
     <t>Bundle.language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Bundle.identifier</t>
@@ -1186,46 +1189,15 @@
     <t>Drives the behavior associated with this message.</t>
   </si>
   <si>
-    <t>One of the message events defined as part of this version of FHIR.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/message-events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x]:eventCoding</t>
-  </si>
-  <si>
-    <t>eventCoding</t>
-  </si>
-  <si>
-    <t>Code for the event this message represents or link to event definition</t>
-  </si>
-  <si>
     <t>http://medcomfhir.dk/ig/terminology/ValueSet/medcom-messaging-messageTypes</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.id</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].id</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.extension</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].extension</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.system</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].system</t>
   </si>
   <si>
@@ -1244,9 +1216,6 @@
     <t>Coding.system</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.version</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].version</t>
   </si>
   <si>
@@ -1262,9 +1231,6 @@
     <t>Coding.version</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.code</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].code</t>
   </si>
   <si>
@@ -1280,9 +1246,6 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.display</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].display</t>
   </si>
   <si>
@@ -1296,9 +1259,6 @@
   </si>
   <si>
     <t>Coding.display</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x]:eventCoding.userSelected</t>
   </si>
   <si>
     <t>MessageHeader.event[x].userSelected</t>
@@ -1342,6 +1302,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>MessageHeader.destination.id</t>
   </si>
   <si>
@@ -1449,6 +1412,9 @@
     <t>MessageHeader.destination:primary.id</t>
   </si>
   <si>
+    <t>MessageHeader.destination:primary.extension</t>
+  </si>
+  <si>
     <t>MessageHeader.destination:primary.extension:use</t>
   </si>
   <si>
@@ -1495,15 +1461,6 @@
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding</t>
-  </si>
-  <si>
-    <t>valueCoding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1512,19 +1469,22 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.id</t>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:primary.extension:use.value[x].id</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].id</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.extension</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].extension</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].extension</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.system</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].system</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].system</t>
@@ -1533,25 +1493,25 @@
     <t>http://medcomfhir.dk/ig/terminology/CodeSystem/medcom-messaging-destinationUse</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.version</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].version</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].version</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.code</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].code</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].code</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.display</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].display</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].display</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.userSelected</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].userSelected</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].userSelected</t>
@@ -1588,6 +1548,9 @@
     <t>MessageHeader.destination:cc.id</t>
   </si>
   <si>
+    <t>MessageHeader.destination:cc.extension</t>
+  </si>
+  <si>
     <t>MessageHeader.destination:cc.extension:use</t>
   </si>
   <si>
@@ -1601,9 +1564,6 @@
   </si>
   <si>
     <t>MessageHeader.destination:cc.extension:use.value[x]</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1612,25 +1572,25 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.id</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.extension</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.system</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.version</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.code</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.display</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.userSelected</t>
+    <t>MessageHeader.destination:cc.extension:use.value[x].id</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].extension</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].system</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].version</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].code</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].display</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].userSelected</t>
   </si>
   <si>
     <t>MessageHeader.destination:cc.modifierExtension</t>
@@ -2373,7 +2333,7 @@
         <v>2</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="45">
@@ -2381,7 +2341,7 @@
         <v>4</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46">
@@ -2397,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48">
@@ -2457,7 +2417,7 @@
         <v>22</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="56">
@@ -2493,7 +2453,7 @@
         <v>30</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="61">
@@ -2501,7 +2461,7 @@
         <v>32</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="62">
@@ -2527,20 +2487,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK162"/>
+  <dimension ref="A1:AK161"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.52734375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="77.984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="55.1171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="38.81640625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="14.625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="37.78515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="58.6875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="48.6953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="34.21875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="12.74609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="12.3828125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2549,21 +2509,21 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="98.1796875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="163.2734375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="81.2578125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="26.125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.98828125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="34.8046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.5" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="86.1796875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="144.1953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="69.94140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="23.56640625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="14.7578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="30.28125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.046875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
   <sheetData>
@@ -5587,7 +5547,7 @@
         <v>108</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="AB29" t="s" s="2">
         <v>74</v>
@@ -5625,10 +5585,10 @@
         <v>209</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" t="s" s="2">
@@ -5651,16 +5611,16 @@
         <v>84</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" t="s" s="2">
@@ -5710,7 +5670,7 @@
         <v>74</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>75</v>
@@ -5730,10 +5690,10 @@
         <v>209</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" t="s" s="2">
@@ -5759,13 +5719,13 @@
         <v>103</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" t="s" s="2">
@@ -5776,7 +5736,7 @@
         <v>74</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>74</v>
@@ -5794,10 +5754,10 @@
         <v>160</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AB31" t="s" s="2">
         <v>74</v>
@@ -5815,7 +5775,7 @@
         <v>74</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>83</v>
@@ -5835,10 +5795,10 @@
         <v>209</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5861,16 +5821,16 @@
         <v>84</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" t="s" s="2">
@@ -5920,7 +5880,7 @@
         <v>74</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>75</v>
@@ -5940,10 +5900,10 @@
         <v>209</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" t="s" s="2">
@@ -5966,16 +5926,16 @@
         <v>84</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" t="s" s="2">
@@ -6025,7 +5985,7 @@
         <v>74</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>75</v>
@@ -6034,7 +5994,7 @@
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>95</v>
@@ -6045,10 +6005,10 @@
         <v>209</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" t="s" s="2">
@@ -6074,13 +6034,13 @@
         <v>139</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" t="s" s="2">
@@ -6130,7 +6090,7 @@
         <v>74</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>75</v>
@@ -6150,10 +6110,10 @@
         <v>209</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" t="s" s="2">
@@ -6253,10 +6213,10 @@
         <v>209</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" t="s" s="2">
@@ -6358,10 +6318,10 @@
         <v>209</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" t="s" s="2">
@@ -6465,10 +6425,10 @@
         <v>209</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" t="s" s="2">
@@ -6494,10 +6454,10 @@
         <v>143</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" s="2"/>
@@ -6548,7 +6508,7 @@
         <v>74</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>83</v>
@@ -6568,10 +6528,10 @@
         <v>209</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" t="s" s="2">
@@ -6597,10 +6557,10 @@
         <v>97</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -6651,7 +6611,7 @@
         <v>74</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>83</v>
@@ -6671,10 +6631,10 @@
         <v>209</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6700,10 +6660,10 @@
         <v>139</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -6754,7 +6714,7 @@
         <v>74</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>75</v>
@@ -6766,7 +6726,7 @@
         <v>74</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="41">
@@ -6774,10 +6734,10 @@
         <v>209</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" t="s" s="2">
@@ -6877,10 +6837,10 @@
         <v>209</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" t="s" s="2">
@@ -6982,10 +6942,10 @@
         <v>209</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" t="s" s="2">
@@ -7089,10 +7049,10 @@
         <v>209</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" t="s" s="2">
@@ -7118,10 +7078,10 @@
         <v>77</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" s="2"/>
@@ -7172,7 +7132,7 @@
         <v>74</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>75</v>
@@ -7192,10 +7152,10 @@
         <v>209</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" t="s" s="2">
@@ -7221,13 +7181,13 @@
         <v>97</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P45" s="2"/>
       <c r="Q45" t="s" s="2">
@@ -7277,7 +7237,7 @@
         <v>74</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>75</v>
@@ -7297,10 +7257,10 @@
         <v>209</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" t="s" s="2">
@@ -7326,10 +7286,10 @@
         <v>120</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" s="2"/>
@@ -7380,7 +7340,7 @@
         <v>74</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AH46" t="s" s="2">
         <v>75</v>
@@ -7400,10 +7360,10 @@
         <v>209</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" t="s" s="2">
@@ -7429,10 +7389,10 @@
         <v>139</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -7483,7 +7443,7 @@
         <v>74</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>75</v>
@@ -7492,7 +7452,7 @@
         <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>95</v>
@@ -7503,10 +7463,10 @@
         <v>209</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s" s="2">
@@ -7606,10 +7566,10 @@
         <v>209</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" t="s" s="2">
@@ -7711,10 +7671,10 @@
         <v>209</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7818,10 +7778,10 @@
         <v>209</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7847,13 +7807,13 @@
         <v>103</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P51" s="2"/>
       <c r="Q51" t="s" s="2">
@@ -7882,10 +7842,10 @@
         <v>160</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AA51" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AB51" t="s" s="2">
         <v>74</v>
@@ -7903,7 +7863,7 @@
         <v>74</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>75</v>
@@ -7923,10 +7883,10 @@
         <v>209</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" t="s" s="2">
@@ -7949,16 +7909,16 @@
         <v>84</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P52" s="2"/>
       <c r="Q52" t="s" s="2">
@@ -8008,7 +7968,7 @@
         <v>74</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>75</v>
@@ -8028,10 +7988,10 @@
         <v>209</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" t="s" s="2">
@@ -8057,10 +8017,10 @@
         <v>139</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
@@ -8111,7 +8071,7 @@
         <v>74</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>75</v>
@@ -8120,7 +8080,7 @@
         <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>95</v>
@@ -8131,10 +8091,10 @@
         <v>209</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -8234,10 +8194,10 @@
         <v>209</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8339,10 +8299,10 @@
         <v>209</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8446,10 +8406,10 @@
         <v>209</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8475,10 +8435,10 @@
         <v>103</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -8508,10 +8468,10 @@
         <v>160</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AA57" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AB57" t="s" s="2">
         <v>74</v>
@@ -8529,7 +8489,7 @@
         <v>74</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>83</v>
@@ -8549,10 +8509,10 @@
         <v>209</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" t="s" s="2">
@@ -8578,13 +8538,13 @@
         <v>97</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P58" s="2"/>
       <c r="Q58" t="s" s="2">
@@ -8634,7 +8594,7 @@
         <v>74</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>83</v>
@@ -8654,10 +8614,10 @@
         <v>209</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" t="s" s="2">
@@ -8683,10 +8643,10 @@
         <v>143</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" s="2"/>
@@ -8737,7 +8697,7 @@
         <v>74</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>75</v>
@@ -8757,10 +8717,10 @@
         <v>209</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" t="s" s="2">
@@ -8783,13 +8743,13 @@
         <v>84</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" s="2"/>
@@ -8840,7 +8800,7 @@
         <v>74</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>75</v>
@@ -8860,10 +8820,10 @@
         <v>209</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8889,10 +8849,10 @@
         <v>143</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" s="2"/>
@@ -8943,7 +8903,7 @@
         <v>74</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>75</v>
@@ -8963,10 +8923,10 @@
         <v>209</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" t="s" s="2">
@@ -8992,10 +8952,10 @@
         <v>143</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" s="2"/>
@@ -9046,7 +9006,7 @@
         <v>74</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>75</v>
@@ -9066,10 +9026,10 @@
         <v>209</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" t="s" s="2">
@@ -9095,10 +9055,10 @@
         <v>139</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" s="2"/>
@@ -9149,7 +9109,7 @@
         <v>74</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>75</v>
@@ -9158,7 +9118,7 @@
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>95</v>
@@ -9169,10 +9129,10 @@
         <v>209</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" t="s" s="2">
@@ -9272,10 +9232,10 @@
         <v>209</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" t="s" s="2">
@@ -9377,10 +9337,10 @@
         <v>209</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" t="s" s="2">
@@ -9484,10 +9444,10 @@
         <v>209</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" t="s" s="2">
@@ -9513,10 +9473,10 @@
         <v>143</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" s="2"/>
@@ -9567,7 +9527,7 @@
         <v>74</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>83</v>
@@ -9587,10 +9547,10 @@
         <v>209</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" t="s" s="2">
@@ -9616,10 +9576,10 @@
         <v>97</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" s="2"/>
@@ -9670,7 +9630,7 @@
         <v>74</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AH68" t="s" s="2">
         <v>75</v>
@@ -9690,10 +9650,10 @@
         <v>209</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" t="s" s="2">
@@ -9719,13 +9679,13 @@
         <v>143</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P69" s="2"/>
       <c r="Q69" t="s" s="2">
@@ -9775,7 +9735,7 @@
         <v>74</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AH69" t="s" s="2">
         <v>75</v>
@@ -9795,10 +9755,10 @@
         <v>209</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" t="s" s="2">
@@ -9821,16 +9781,16 @@
         <v>84</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P70" s="2"/>
       <c r="Q70" t="s" s="2">
@@ -9880,7 +9840,7 @@
         <v>74</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>75</v>
@@ -9900,10 +9860,10 @@
         <v>209</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" t="s" s="2">
@@ -9929,13 +9889,13 @@
         <v>120</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P71" s="2"/>
       <c r="Q71" t="s" s="2">
@@ -9985,7 +9945,7 @@
         <v>74</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>75</v>
@@ -10005,10 +9965,10 @@
         <v>209</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" t="s" s="2">
@@ -10031,19 +9991,19 @@
         <v>84</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P72" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q72" t="s" s="2">
         <v>74</v>
@@ -10092,7 +10052,7 @@
         <v>74</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>75</v>
@@ -10109,13 +10069,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" t="s" s="2">
@@ -10141,10 +10101,10 @@
         <v>77</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" s="2"/>
@@ -10195,7 +10155,7 @@
         <v>74</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>75</v>
@@ -10212,13 +10172,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" t="s" s="2">
@@ -10244,7 +10204,7 @@
         <v>85</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>87</v>
@@ -10317,13 +10277,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" t="s" s="2">
@@ -10420,13 +10380,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" t="s" s="2">
@@ -10525,13 +10485,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" t="s" s="2">
@@ -10595,7 +10555,7 @@
         <v>108</v>
       </c>
       <c r="AA77" t="s" s="2">
-        <v>109</v>
+        <v>222</v>
       </c>
       <c r="AB77" t="s" s="2">
         <v>74</v>
@@ -10630,13 +10590,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" t="s" s="2">
@@ -10662,7 +10622,7 @@
         <v>113</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>115</v>
@@ -10735,13 +10695,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" t="s" s="2">
@@ -10840,13 +10800,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" t="s" s="2">
@@ -10945,13 +10905,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" t="s" s="2">
@@ -11052,13 +11012,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" t="s" s="2">
@@ -11072,7 +11032,7 @@
         <v>83</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>74</v>
@@ -11084,16 +11044,16 @@
         <v>183</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P82" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q82" t="s" s="2">
         <v>74</v>
@@ -11118,11 +11078,9 @@
         <v>74</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="Z82" s="2"/>
       <c r="AA82" t="s" s="2">
         <v>375</v>
       </c>
@@ -11130,17 +11088,19 @@
         <v>74</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AD82" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AE82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>377</v>
+        <v>74</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>83</v>
@@ -11157,51 +11117,45 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="D83" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="D83" s="2"/>
       <c r="E83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>380</v>
+        <v>144</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" s="2"/>
       <c r="Q83" t="s" s="2">
         <v>74</v>
       </c>
@@ -11225,11 +11179,13 @@
         <v>74</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Z83" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AA83" t="s" s="2">
-        <v>381</v>
+        <v>74</v>
       </c>
       <c r="AB83" t="s" s="2">
         <v>74</v>
@@ -11247,10 +11203,10 @@
         <v>74</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>369</v>
+        <v>146</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>83</v>
@@ -11259,29 +11215,29 @@
         <v>74</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>74</v>
@@ -11293,15 +11249,17 @@
         <v>74</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O84" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P84" s="2"/>
       <c r="Q84" t="s" s="2">
         <v>74</v>
@@ -11338,53 +11296,53 @@
         <v>74</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="AD84" t="s" s="2">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="AE84" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AH84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" t="s" s="2">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>74</v>
@@ -11393,21 +11351,23 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>128</v>
+        <v>379</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>148</v>
+        <v>380</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P85" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="Q85" t="s" s="2">
         <v>74</v>
       </c>
@@ -11443,42 +11403,42 @@
         <v>74</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="AD85" t="s" s="2">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="AE85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>149</v>
+        <v>383</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>132</v>
+        <v>95</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" t="s" s="2">
@@ -11501,20 +11461,18 @@
         <v>84</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="P86" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="P86" s="2"/>
       <c r="Q86" t="s" s="2">
         <v>74</v>
       </c>
@@ -11562,7 +11520,7 @@
         <v>74</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>75</v>
@@ -11579,13 +11537,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
@@ -11593,7 +11551,7 @@
       </c>
       <c r="F87" s="2"/>
       <c r="G87" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>83</v>
@@ -11608,18 +11566,18 @@
         <v>84</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="P87" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="Q87" t="s" s="2">
         <v>74</v>
       </c>
@@ -11667,7 +11625,7 @@
         <v>74</v>
       </c>
       <c r="AG87" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="AH87" t="s" s="2">
         <v>75</v>
@@ -11684,13 +11642,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" t="s" s="2">
@@ -11698,7 +11656,7 @@
       </c>
       <c r="F88" s="2"/>
       <c r="G88" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>83</v>
@@ -11713,17 +11671,17 @@
         <v>84</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="Q88" t="s" s="2">
         <v>74</v>
@@ -11772,7 +11730,7 @@
         <v>74</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="AH88" t="s" s="2">
         <v>75</v>
@@ -11789,13 +11747,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -11818,17 +11776,19 @@
         <v>84</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>143</v>
+        <v>400</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P89" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="Q89" t="s" s="2">
         <v>74</v>
@@ -11877,7 +11837,7 @@
         <v>74</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>75</v>
@@ -11894,13 +11854,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -11908,10 +11868,10 @@
       </c>
       <c r="F90" s="2"/>
       <c r="G90" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>74</v>
@@ -11923,19 +11883,19 @@
         <v>84</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>413</v>
+        <v>139</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="P90" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="Q90" t="s" s="2">
         <v>74</v>
@@ -11972,25 +11932,23 @@
         <v>74</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="AD90" s="2"/>
       <c r="AE90" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>74</v>
+        <v>412</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>74</v>
@@ -12001,13 +11959,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -12015,10 +11973,10 @@
       </c>
       <c r="F91" s="2"/>
       <c r="G91" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>74</v>
@@ -12027,23 +11985,19 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>420</v>
+        <v>144</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="P91" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O91" s="2"/>
+      <c r="P91" s="2"/>
       <c r="Q91" t="s" s="2">
         <v>74</v>
       </c>
@@ -12079,40 +12033,42 @@
         <v>74</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AD91" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AE91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>377</v>
+        <v>74</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>419</v>
+        <v>146</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -12120,10 +12076,10 @@
       </c>
       <c r="F92" s="2"/>
       <c r="G92" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>74</v>
@@ -12135,13 +12091,13 @@
         <v>74</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>144</v>
+        <v>415</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>145</v>
+        <v>416</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" s="2"/>
@@ -12180,44 +12136,44 @@
         <v>74</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="AD92" s="2"/>
       <c r="AE92" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="D93" s="2"/>
+        <v>414</v>
+      </c>
+      <c r="D93" t="s" s="2">
+        <v>418</v>
+      </c>
       <c r="E93" t="s" s="2">
         <v>74</v>
       </c>
@@ -12226,10 +12182,10 @@
         <v>83</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>74</v>
@@ -12238,13 +12194,13 @@
         <v>74</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>127</v>
+        <v>419</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
@@ -12283,14 +12239,16 @@
         <v>74</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="AD93" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AE93" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>149</v>
@@ -12302,7 +12260,7 @@
         <v>76</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>74</v>
+        <v>422</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>132</v>
@@ -12310,47 +12268,49 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="D94" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J94" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="J94" t="s" s="2">
-        <v>74</v>
-      </c>
       <c r="K94" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>431</v>
+        <v>127</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>432</v>
+        <v>152</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O94" s="2"/>
-      <c r="P94" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q94" t="s" s="2">
         <v>74</v>
       </c>
@@ -12398,7 +12358,7 @@
         <v>74</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>75</v>
@@ -12407,7 +12367,7 @@
         <v>76</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>434</v>
+        <v>74</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>132</v>
@@ -12415,48 +12375,46 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>152</v>
+        <v>425</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
-        <v>136</v>
+        <v>427</v>
       </c>
       <c r="Q95" t="s" s="2">
         <v>74</v>
@@ -12505,30 +12463,30 @@
         <v>74</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>154</v>
+        <v>424</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>132</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -12551,17 +12509,17 @@
         <v>84</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>143</v>
+        <v>429</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="Q96" t="s" s="2">
         <v>74</v>
@@ -12610,7 +12568,7 @@
         <v>74</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>75</v>
@@ -12627,13 +12585,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -12641,7 +12599,7 @@
       </c>
       <c r="F97" s="2"/>
       <c r="G97" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>83</v>
@@ -12656,17 +12614,19 @@
         <v>84</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P97" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="Q97" t="s" s="2">
         <v>74</v>
@@ -12715,10 +12675,10 @@
         <v>74</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>83</v>
@@ -12732,13 +12692,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -12746,7 +12706,7 @@
       </c>
       <c r="F98" s="2"/>
       <c r="G98" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>83</v>
@@ -12761,19 +12721,17 @@
         <v>84</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="Q98" t="s" s="2">
         <v>74</v>
@@ -12822,10 +12780,10 @@
         <v>74</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>83</v>
@@ -12839,27 +12797,29 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="D99" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="D99" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="E99" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I99" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J99" t="s" s="2">
         <v>74</v>
@@ -12868,17 +12828,19 @@
         <v>84</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>452</v>
+        <v>139</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>453</v>
+        <v>407</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P99" t="s" s="2">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="Q99" t="s" s="2">
         <v>74</v>
@@ -12927,13 +12889,13 @@
         <v>74</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>451</v>
+        <v>406</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>74</v>
@@ -12944,51 +12906,45 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="D100" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>420</v>
+        <v>144</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" s="2"/>
       <c r="Q100" t="s" s="2">
         <v>74</v>
       </c>
@@ -13036,41 +12992,41 @@
         <v>74</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>419</v>
+        <v>146</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>74</v>
@@ -13082,15 +13038,17 @@
         <v>74</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O101" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P101" s="2"/>
       <c r="Q101" t="s" s="2">
         <v>74</v>
@@ -13127,45 +13085,43 @@
         <v>74</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="AD101" s="2"/>
       <c r="AE101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="D102" t="s" s="2">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E102" t="s" s="2">
         <v>74</v>
@@ -13187,13 +13143,13 @@
         <v>74</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" s="2"/>
@@ -13253,7 +13209,7 @@
         <v>76</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>132</v>
@@ -13261,13 +13217,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -13364,13 +13320,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -13396,10 +13352,10 @@
         <v>127</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
@@ -13467,13 +13423,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -13499,13 +13455,13 @@
         <v>97</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P105" s="2"/>
       <c r="Q105" t="s" s="2">
@@ -13513,7 +13469,7 @@
       </c>
       <c r="R105" s="2"/>
       <c r="S105" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>74</v>
@@ -13555,7 +13511,7 @@
         <v>74</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>83</v>
@@ -13572,13 +13528,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -13604,10 +13560,10 @@
         <v>183</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
@@ -13619,7 +13575,7 @@
         <v>74</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>74</v>
+        <v>464</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>74</v>
@@ -13646,17 +13602,19 @@
         <v>74</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AD106" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AE106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>377</v>
+        <v>74</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>75</v>
@@ -13673,23 +13631,21 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="D107" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>83</v>
@@ -13704,13 +13660,13 @@
         <v>74</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>473</v>
+        <v>144</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>474</v>
+        <v>145</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
@@ -13722,7 +13678,7 @@
         <v>74</v>
       </c>
       <c r="T107" t="s" s="2">
-        <v>478</v>
+        <v>74</v>
       </c>
       <c r="U107" t="s" s="2">
         <v>74</v>
@@ -13761,7 +13717,7 @@
         <v>74</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>475</v>
+        <v>146</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>75</v>
@@ -13773,29 +13729,29 @@
         <v>74</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>74</v>
@@ -13807,15 +13763,17 @@
         <v>74</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P108" s="2"/>
       <c r="Q108" t="s" s="2">
         <v>74</v>
@@ -13852,53 +13810,53 @@
         <v>74</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="AD108" t="s" s="2">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="AE108" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="F109" s="2"/>
       <c r="G109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>74</v>
@@ -13907,21 +13865,23 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>128</v>
+        <v>379</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>148</v>
+        <v>380</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P109" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="Q109" t="s" s="2">
         <v>74</v>
       </c>
@@ -13930,7 +13890,7 @@
         <v>74</v>
       </c>
       <c r="T109" t="s" s="2">
-        <v>74</v>
+        <v>472</v>
       </c>
       <c r="U109" t="s" s="2">
         <v>74</v>
@@ -13957,42 +13917,42 @@
         <v>74</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="AD109" t="s" s="2">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="AE109" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>149</v>
+        <v>383</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>132</v>
+        <v>95</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -14015,20 +13975,18 @@
         <v>84</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="P110" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="P110" s="2"/>
       <c r="Q110" t="s" s="2">
         <v>74</v>
       </c>
@@ -14037,7 +13995,7 @@
         <v>74</v>
       </c>
       <c r="T110" t="s" s="2">
-        <v>485</v>
+        <v>74</v>
       </c>
       <c r="U110" t="s" s="2">
         <v>74</v>
@@ -14076,7 +14034,7 @@
         <v>74</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>75</v>
@@ -14093,13 +14051,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -14122,18 +14080,18 @@
         <v>84</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="P111" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="Q111" t="s" s="2">
         <v>74</v>
       </c>
@@ -14181,7 +14139,7 @@
         <v>74</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>75</v>
@@ -14198,13 +14156,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -14227,17 +14185,17 @@
         <v>84</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="Q112" t="s" s="2">
         <v>74</v>
@@ -14286,7 +14244,7 @@
         <v>74</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="AH112" t="s" s="2">
         <v>75</v>
@@ -14303,13 +14261,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -14332,17 +14290,19 @@
         <v>84</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>143</v>
+        <v>400</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O113" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O113" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P113" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="Q113" t="s" s="2">
         <v>74</v>
@@ -14391,7 +14351,7 @@
         <v>74</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AH113" t="s" s="2">
         <v>75</v>
@@ -14408,48 +14368,48 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>493</v>
+        <v>423</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>413</v>
+        <v>127</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>414</v>
+        <v>152</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>415</v>
+        <v>153</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>416</v>
+        <v>130</v>
       </c>
       <c r="P114" t="s" s="2">
-        <v>417</v>
+        <v>136</v>
       </c>
       <c r="Q114" t="s" s="2">
         <v>74</v>
@@ -14498,65 +14458,63 @@
         <v>74</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>418</v>
+        <v>154</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>95</v>
+        <v>132</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>152</v>
+        <v>425</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
-        <v>136</v>
+        <v>427</v>
       </c>
       <c r="Q115" t="s" s="2">
         <v>74</v>
@@ -14605,30 +14563,30 @@
         <v>74</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>154</v>
+        <v>424</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>132</v>
+        <v>95</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -14651,17 +14609,17 @@
         <v>84</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>143</v>
+        <v>429</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="Q116" t="s" s="2">
         <v>74</v>
@@ -14710,7 +14668,7 @@
         <v>74</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>75</v>
@@ -14727,13 +14685,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -14741,13 +14699,13 @@
       </c>
       <c r="F117" s="2"/>
       <c r="G117" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J117" t="s" s="2">
         <v>74</v>
@@ -14756,17 +14714,19 @@
         <v>84</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P117" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="Q117" t="s" s="2">
         <v>74</v>
@@ -14815,10 +14775,10 @@
         <v>74</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>83</v>
@@ -14832,13 +14792,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -14861,19 +14821,17 @@
         <v>84</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>446</v>
+        <v>486</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>447</v>
+        <v>487</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="Q118" t="s" s="2">
         <v>74</v>
@@ -14922,10 +14880,10 @@
         <v>74</v>
       </c>
       <c r="AG118" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>83</v>
@@ -14939,27 +14897,29 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="D119" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="D119" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="E119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I119" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J119" t="s" s="2">
         <v>74</v>
@@ -14968,17 +14928,19 @@
         <v>84</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>499</v>
+        <v>139</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>500</v>
+        <v>407</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O119" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P119" t="s" s="2">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="Q119" t="s" s="2">
         <v>74</v>
@@ -15027,13 +14989,13 @@
         <v>74</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>451</v>
+        <v>406</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>74</v>
@@ -15044,17 +15006,15 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="D120" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
         <v>74</v>
       </c>
@@ -15063,7 +15023,7 @@
         <v>75</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>74</v>
@@ -15072,23 +15032,19 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>420</v>
+        <v>144</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="P120" t="s" s="2">
-        <v>423</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" s="2"/>
       <c r="Q120" t="s" s="2">
         <v>74</v>
       </c>
@@ -15136,41 +15092,41 @@
         <v>74</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>419</v>
+        <v>146</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>74</v>
@@ -15182,15 +15138,17 @@
         <v>74</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O121" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P121" s="2"/>
       <c r="Q121" t="s" s="2">
         <v>74</v>
@@ -15227,45 +15185,43 @@
         <v>74</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="AD121" s="2"/>
       <c r="AE121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AH121" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="D122" t="s" s="2">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="E122" t="s" s="2">
         <v>74</v>
@@ -15287,13 +15243,13 @@
         <v>74</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" s="2"/>
@@ -15353,7 +15309,7 @@
         <v>76</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>132</v>
@@ -15361,13 +15317,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -15464,13 +15420,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -15496,10 +15452,10 @@
         <v>127</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" s="2"/>
@@ -15567,13 +15523,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -15599,13 +15555,13 @@
         <v>97</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="P125" s="2"/>
       <c r="Q125" t="s" s="2">
@@ -15613,7 +15569,7 @@
       </c>
       <c r="R125" s="2"/>
       <c r="S125" t="s" s="2">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>74</v>
@@ -15655,7 +15611,7 @@
         <v>74</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>83</v>
@@ -15672,13 +15628,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -15704,10 +15660,10 @@
         <v>183</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" s="2"/>
@@ -15719,7 +15675,7 @@
         <v>74</v>
       </c>
       <c r="T126" t="s" s="2">
-        <v>74</v>
+        <v>497</v>
       </c>
       <c r="U126" t="s" s="2">
         <v>74</v>
@@ -15746,17 +15702,19 @@
         <v>74</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AD126" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AE126" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>377</v>
+        <v>74</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="AH126" t="s" s="2">
         <v>75</v>
@@ -15773,23 +15731,21 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="D127" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
         <v>74</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>83</v>
@@ -15804,13 +15760,13 @@
         <v>74</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>183</v>
+        <v>143</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>473</v>
+        <v>144</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>474</v>
+        <v>145</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" s="2"/>
@@ -15822,7 +15778,7 @@
         <v>74</v>
       </c>
       <c r="T127" t="s" s="2">
-        <v>510</v>
+        <v>74</v>
       </c>
       <c r="U127" t="s" s="2">
         <v>74</v>
@@ -15861,7 +15817,7 @@
         <v>74</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>475</v>
+        <v>146</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>75</v>
@@ -15873,29 +15829,29 @@
         <v>74</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>74</v>
@@ -15907,15 +15863,17 @@
         <v>74</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O128" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P128" s="2"/>
       <c r="Q128" t="s" s="2">
         <v>74</v>
@@ -15952,53 +15910,53 @@
         <v>74</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="AD128" t="s" s="2">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="AE128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>74</v>
+        <v>181</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK128" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="F129" s="2"/>
       <c r="G129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>74</v>
@@ -16007,21 +15965,23 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>128</v>
+        <v>379</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>148</v>
+        <v>380</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="P129" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="P129" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="Q129" t="s" s="2">
         <v>74</v>
       </c>
@@ -16030,7 +15990,7 @@
         <v>74</v>
       </c>
       <c r="T129" t="s" s="2">
-        <v>74</v>
+        <v>472</v>
       </c>
       <c r="U129" t="s" s="2">
         <v>74</v>
@@ -16057,42 +16017,42 @@
         <v>74</v>
       </c>
       <c r="AC129" t="s" s="2">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="AD129" t="s" s="2">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="AE129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>149</v>
+        <v>383</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>132</v>
+        <v>95</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -16115,20 +16075,18 @@
         <v>84</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="P130" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="P130" s="2"/>
       <c r="Q130" t="s" s="2">
         <v>74</v>
       </c>
@@ -16137,7 +16095,7 @@
         <v>74</v>
       </c>
       <c r="T130" t="s" s="2">
-        <v>485</v>
+        <v>74</v>
       </c>
       <c r="U130" t="s" s="2">
         <v>74</v>
@@ -16176,7 +16134,7 @@
         <v>74</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>75</v>
@@ -16193,13 +16151,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -16222,18 +16180,18 @@
         <v>84</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="P131" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="Q131" t="s" s="2">
         <v>74</v>
       </c>
@@ -16281,7 +16239,7 @@
         <v>74</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>75</v>
@@ -16298,13 +16256,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -16327,17 +16285,17 @@
         <v>84</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="Q132" t="s" s="2">
         <v>74</v>
@@ -16386,7 +16344,7 @@
         <v>74</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>75</v>
@@ -16403,13 +16361,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -16432,17 +16390,19 @@
         <v>84</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>143</v>
+        <v>400</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O133" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P133" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="Q133" t="s" s="2">
         <v>74</v>
@@ -16491,7 +16451,7 @@
         <v>74</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>75</v>
@@ -16508,48 +16468,48 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>493</v>
+        <v>423</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="F134" s="2"/>
       <c r="G134" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K134" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>413</v>
+        <v>127</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>414</v>
+        <v>152</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>415</v>
+        <v>153</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>416</v>
+        <v>130</v>
       </c>
       <c r="P134" t="s" s="2">
-        <v>417</v>
+        <v>136</v>
       </c>
       <c r="Q134" t="s" s="2">
         <v>74</v>
@@ -16598,65 +16558,63 @@
         <v>74</v>
       </c>
       <c r="AG134" t="s" s="2">
-        <v>418</v>
+        <v>154</v>
       </c>
       <c r="AH134" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>95</v>
+        <v>132</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="F135" s="2"/>
       <c r="G135" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>152</v>
+        <v>425</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
-        <v>136</v>
+        <v>427</v>
       </c>
       <c r="Q135" t="s" s="2">
         <v>74</v>
@@ -16705,30 +16663,30 @@
         <v>74</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>154</v>
+        <v>424</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>132</v>
+        <v>95</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -16751,17 +16709,17 @@
         <v>84</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>143</v>
+        <v>429</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="Q136" t="s" s="2">
         <v>74</v>
@@ -16810,7 +16768,7 @@
         <v>74</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>75</v>
@@ -16827,13 +16785,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -16841,13 +16799,13 @@
       </c>
       <c r="F137" s="2"/>
       <c r="G137" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I137" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J137" t="s" s="2">
         <v>74</v>
@@ -16856,17 +16814,19 @@
         <v>84</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O137" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="O137" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P137" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="Q137" t="s" s="2">
         <v>74</v>
@@ -16915,10 +16875,10 @@
         <v>74</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>83</v>
@@ -16932,13 +16892,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -16961,19 +16921,17 @@
         <v>84</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>446</v>
+        <v>486</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>447</v>
+        <v>510</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O138" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="Q138" t="s" s="2">
         <v>74</v>
@@ -17022,10 +16980,10 @@
         <v>74</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>83</v>
@@ -17039,13 +16997,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -17068,17 +17026,19 @@
         <v>84</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O139" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="P139" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="Q139" t="s" s="2">
         <v>74</v>
@@ -17127,7 +17087,7 @@
         <v>74</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>451</v>
+        <v>511</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>75</v>
@@ -17144,13 +17104,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -17158,13 +17118,13 @@
       </c>
       <c r="F140" s="2"/>
       <c r="G140" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I140" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J140" t="s" s="2">
         <v>74</v>
@@ -17173,19 +17133,19 @@
         <v>84</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="P140" t="s" s="2">
-        <v>455</v>
+        <v>520</v>
       </c>
       <c r="Q140" t="s" s="2">
         <v>74</v>
@@ -17234,7 +17194,7 @@
         <v>74</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>75</v>
@@ -17251,13 +17211,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -17280,19 +17240,19 @@
         <v>84</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="P141" t="s" s="2">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="Q141" t="s" s="2">
         <v>74</v>
@@ -17341,7 +17301,7 @@
         <v>74</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>75</v>
@@ -17358,13 +17318,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -17372,13 +17332,13 @@
       </c>
       <c r="F142" s="2"/>
       <c r="G142" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J142" t="s" s="2">
         <v>74</v>
@@ -17387,19 +17347,17 @@
         <v>84</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>529</v>
+        <v>139</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="Q142" t="s" s="2">
         <v>74</v>
@@ -17448,10 +17406,10 @@
         <v>74</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>83</v>
@@ -17465,13 +17423,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -17479,33 +17437,31 @@
       </c>
       <c r="F143" s="2"/>
       <c r="G143" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I143" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J143" t="s" s="2">
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>538</v>
+        <v>144</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>539</v>
+        <v>145</v>
       </c>
       <c r="O143" s="2"/>
-      <c r="P143" t="s" s="2">
-        <v>540</v>
-      </c>
+      <c r="P143" s="2"/>
       <c r="Q143" t="s" s="2">
         <v>74</v>
       </c>
@@ -17553,10 +17509,10 @@
         <v>74</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>537</v>
+        <v>146</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>83</v>
@@ -17565,29 +17521,29 @@
         <v>74</v>
       </c>
       <c r="AK143" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>74</v>
@@ -17599,15 +17555,17 @@
         <v>74</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O144" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="O144" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P144" s="2"/>
       <c r="Q144" t="s" s="2">
         <v>74</v>
@@ -17656,34 +17614,34 @@
         <v>74</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK144" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" t="s" s="2">
@@ -17696,24 +17654,26 @@
         <v>74</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="L145" t="s" s="2">
         <v>127</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="O145" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="P145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q145" t="s" s="2">
         <v>74</v>
       </c>
@@ -17761,7 +17721,7 @@
         <v>74</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>75</v>
@@ -17778,48 +17738,46 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>74</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>152</v>
+        <v>425</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O146" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
-        <v>136</v>
+        <v>533</v>
       </c>
       <c r="Q146" t="s" s="2">
         <v>74</v>
@@ -17868,30 +17826,30 @@
         <v>74</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>154</v>
+        <v>531</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ146" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK146" t="s" s="2">
-        <v>132</v>
+        <v>95</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -17917,14 +17875,14 @@
         <v>143</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>437</v>
+        <v>535</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="Q147" t="s" s="2">
         <v>74</v>
@@ -17973,7 +17931,7 @@
         <v>74</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>75</v>
@@ -17990,13 +17948,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -18022,14 +17980,14 @@
         <v>143</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="Q148" t="s" s="2">
         <v>74</v>
@@ -18078,7 +18036,7 @@
         <v>74</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>75</v>
@@ -18095,13 +18053,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -18124,17 +18082,17 @@
         <v>84</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>143</v>
+        <v>542</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="Q149" t="s" s="2">
         <v>74</v>
@@ -18183,7 +18141,7 @@
         <v>74</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>551</v>
+        <v>541</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>75</v>
@@ -18200,13 +18158,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -18214,13 +18172,13 @@
       </c>
       <c r="F150" s="2"/>
       <c r="G150" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H150" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I150" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J150" t="s" s="2">
         <v>74</v>
@@ -18229,17 +18187,19 @@
         <v>84</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>555</v>
+        <v>434</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O150" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P150" t="s" s="2">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="Q150" t="s" s="2">
         <v>74</v>
@@ -18288,10 +18248,10 @@
         <v>74</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="AH150" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI150" t="s" s="2">
         <v>83</v>
@@ -18305,13 +18265,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -18319,13 +18279,13 @@
       </c>
       <c r="F151" s="2"/>
       <c r="G151" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I151" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J151" t="s" s="2">
         <v>74</v>
@@ -18334,19 +18294,19 @@
         <v>84</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>449</v>
+        <v>519</v>
       </c>
       <c r="P151" t="s" s="2">
-        <v>562</v>
+        <v>520</v>
       </c>
       <c r="Q151" t="s" s="2">
         <v>74</v>
@@ -18395,10 +18355,10 @@
         <v>74</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>83</v>
@@ -18412,13 +18372,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -18441,19 +18401,17 @@
         <v>84</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>452</v>
+        <v>170</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="O152" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
-        <v>533</v>
+        <v>556</v>
       </c>
       <c r="Q152" t="s" s="2">
         <v>74</v>
@@ -18478,13 +18436,13 @@
         <v>74</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>74</v>
+        <v>557</v>
       </c>
       <c r="AA152" t="s" s="2">
-        <v>74</v>
+        <v>558</v>
       </c>
       <c r="AB152" t="s" s="2">
         <v>74</v>
@@ -18502,7 +18460,7 @@
         <v>74</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>75</v>
@@ -18519,13 +18477,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -18533,13 +18491,13 @@
       </c>
       <c r="F153" s="2"/>
       <c r="G153" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I153" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J153" t="s" s="2">
         <v>74</v>
@@ -18548,18 +18506,16 @@
         <v>84</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="O153" s="2"/>
-      <c r="P153" t="s" s="2">
-        <v>569</v>
-      </c>
+      <c r="P153" s="2"/>
       <c r="Q153" t="s" s="2">
         <v>74</v>
       </c>
@@ -18583,13 +18539,13 @@
         <v>74</v>
       </c>
       <c r="Y153" t="s" s="2">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="Z153" t="s" s="2">
-        <v>570</v>
+        <v>74</v>
       </c>
       <c r="AA153" t="s" s="2">
-        <v>571</v>
+        <v>74</v>
       </c>
       <c r="AB153" t="s" s="2">
         <v>74</v>
@@ -18607,7 +18563,7 @@
         <v>74</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>75</v>
@@ -18624,13 +18580,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -18638,28 +18594,28 @@
       </c>
       <c r="F154" s="2"/>
       <c r="G154" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I154" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>573</v>
+        <v>144</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>574</v>
+        <v>145</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" s="2"/>
@@ -18710,7 +18666,7 @@
         <v>74</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>572</v>
+        <v>146</v>
       </c>
       <c r="AH154" t="s" s="2">
         <v>75</v>
@@ -18722,29 +18678,29 @@
         <v>74</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="F155" s="2"/>
       <c r="G155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I155" t="s" s="2">
         <v>74</v>
@@ -18756,15 +18712,17 @@
         <v>74</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O155" s="2"/>
+        <v>148</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P155" s="2"/>
       <c r="Q155" t="s" s="2">
         <v>74</v>
@@ -18813,34 +18771,34 @@
         <v>74</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>74</v>
+        <v>132</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="F156" s="2"/>
       <c r="G156" t="s" s="2">
@@ -18853,24 +18811,26 @@
         <v>74</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="L156" t="s" s="2">
         <v>127</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="O156" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="P156" s="2"/>
+      <c r="P156" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="Q156" t="s" s="2">
         <v>74</v>
       </c>
@@ -18918,7 +18878,7 @@
         <v>74</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>75</v>
@@ -18935,48 +18895,46 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="F157" s="2"/>
       <c r="G157" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I157" t="s" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>152</v>
+        <v>566</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
-        <v>136</v>
+        <v>568</v>
       </c>
       <c r="Q157" t="s" s="2">
         <v>74</v>
@@ -19025,30 +18983,30 @@
         <v>74</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>154</v>
+        <v>565</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>132</v>
+        <v>95</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -19071,17 +19029,19 @@
         <v>84</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="O158" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="P158" t="s" s="2">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="Q158" t="s" s="2">
         <v>74</v>
@@ -19106,13 +19066,13 @@
         <v>74</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>74</v>
+        <v>574</v>
       </c>
       <c r="AA158" t="s" s="2">
-        <v>74</v>
+        <v>575</v>
       </c>
       <c r="AB158" t="s" s="2">
         <v>74</v>
@@ -19130,7 +19090,7 @@
         <v>74</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="AH158" t="s" s="2">
         <v>83</v>
@@ -19147,13 +19107,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -19161,7 +19121,7 @@
       </c>
       <c r="F159" s="2"/>
       <c r="G159" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>83</v>
@@ -19176,19 +19136,19 @@
         <v>84</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>103</v>
+        <v>577</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="P159" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="Q159" t="s" s="2">
         <v>74</v>
@@ -19213,13 +19173,13 @@
         <v>74</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>587</v>
+        <v>74</v>
       </c>
       <c r="AA159" t="s" s="2">
-        <v>588</v>
+        <v>74</v>
       </c>
       <c r="AB159" t="s" s="2">
         <v>74</v>
@@ -19237,10 +19197,10 @@
         <v>74</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>83</v>
@@ -19254,13 +19214,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -19271,10 +19231,10 @@
         <v>75</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I160" t="s" s="2">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="J160" t="s" s="2">
         <v>74</v>
@@ -19283,19 +19243,19 @@
         <v>84</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="P160" t="s" s="2">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="Q160" t="s" s="2">
         <v>74</v>
@@ -19344,13 +19304,13 @@
         <v>74</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>74</v>
@@ -19361,13 +19321,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -19378,7 +19338,7 @@
         <v>75</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>74</v>
@@ -19390,19 +19350,17 @@
         <v>84</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="Q161" t="s" s="2">
         <v>74</v>
@@ -19451,123 +19409,18 @@
         <v>74</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="D162" s="2"/>
-      <c r="E162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="F162" s="2"/>
-      <c r="G162" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H162" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K162" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L162" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="M162" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="O162" s="2"/>
-      <c r="P162" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="Q162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="R162" s="2"/>
-      <c r="S162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG162" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AH162" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI162" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ162" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK162" t="s" s="2">
         <v>95</v>
       </c>
     </row>
